--- a/data/reports/PHASE_11_5_CANDIDATES.xlsx
+++ b/data/reports/PHASE_11_5_CANDIDATES.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C2" t="n">
         <v>25</v>
@@ -468,42 +468,42 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>52.35</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>51.8</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>379</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
@@ -512,347 +512,347 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>199</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>50.8</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>177</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>101</v>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>50.4</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>399</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>50.35</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>50.35</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>189</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>50.3</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>50.1</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>369</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>50</v>
+        <v>49.85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>389</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>49.85</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C14" t="n">
         <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>378</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>49.65</v>
+        <v>49.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>699</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>49.6</v>
+        <v>49.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>339</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>49.6</v>
+        <v>49.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>49.55</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>799</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C20" t="n">
         <v>17</v>
@@ -861,32 +861,32 @@
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>49.55</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>49.5</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="22">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C22" t="n">
         <v>21</v>
@@ -908,86 +908,86 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>49.35</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>239</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>49.2</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D24" t="n">
         <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>49.15</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>149</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C25" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" t="n">
         <v>2</v>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
       <c r="F25" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>377</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C26" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D26" t="n">
         <v>6</v>
@@ -996,117 +996,117 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>48.65</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>158</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>48.45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>48.15</v>
+        <v>47.95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>779</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>48.1</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>789</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C31" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>48.1</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="32">
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1128,237 +1128,237 @@
         <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>48.1</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>899</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C33" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>48.05</v>
+        <v>47.65</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>157</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C34" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>48</v>
+        <v>47.65</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>999</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C35" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>47.95</v>
+        <v>47.55</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>269</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C36" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D36" t="n">
         <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>47.95</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>679</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>99</v>
       </c>
       <c r="C37" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D37" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>47.9</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C38" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D38" t="n">
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>47.85</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C39" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>47.55</v>
+        <v>47.15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>337</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C40" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>47.5</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C41" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>47.45</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>499</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C42" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>47.4</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>388</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C43" t="n">
         <v>21</v>
@@ -1370,130 +1370,130 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>47.35</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>338</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C44" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>47.25</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>669</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C45" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>47.25</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C46" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D46" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>46.9</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>359</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C47" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D47" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>079</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C48" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D48" t="n">
         <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>689</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C49" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -1502,224 +1502,224 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>46.65</v>
+        <v>46.55</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>358</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C50" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>46.65</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>469</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C51" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>46.6</v>
+        <v>46.35</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>778</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>98</v>
       </c>
       <c r="C52" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>46.55</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>017</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C53" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>46.5</v>
+        <v>46.25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>889</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C54" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>46.35</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>019</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C55" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>46.35</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>039</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C56" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>46.35</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>357</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C57" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>46.3</v>
+        <v>46.05</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C58" t="n">
         <v>20</v>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>46.25</v>
+        <v>46.05</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>077</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C59" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D59" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
         <v>46.05</v>
@@ -1728,23 +1728,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>188</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C60" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D60" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>46</v>
+        <v>46.05</v>
       </c>
     </row>
     <row r="61">
@@ -1772,124 +1772,124 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C62" t="n">
         <v>21</v>
       </c>
       <c r="D62" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>45.95</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>099</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C63" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>45.9</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>349</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C64" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>45.85</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C65" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
-        <v>45.85</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>96</v>
       </c>
       <c r="C66" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>078</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C67" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D67" t="n">
         <v>11</v>
@@ -1898,67 +1898,67 @@
         <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>45.8</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>229</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C68" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D68" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>45.65</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>168</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C69" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>589</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C70" t="n">
         <v>19</v>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -1970,281 +1970,281 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>368</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C71" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>45.25</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>777</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C72" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D72" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>45.2</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>367</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C73" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>45.15</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>019</t>
+          <t>238</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C74" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D74" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>45.15</v>
+        <v>45.35</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>237</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>91</v>
       </c>
       <c r="C75" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E75" t="n">
         <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C76" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>45.05</v>
+        <v>45.25</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C77" t="n">
         <v>19</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>45.05</v>
+        <v>45.25</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C78" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>45</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>249</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C79" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D79" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E79" t="n">
         <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>039</t>
+          <t>479</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C80" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D80" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>44.95</v>
+        <v>45.05</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>156</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C81" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D81" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
-        <v>44.8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>037</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
-        <v>44.75</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>788</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C83" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D83" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -2278,64 +2278,64 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>579</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C85" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>44.55</v>
+        <v>44.65</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>078</t>
+          <t>578</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C86" t="n">
         <v>20</v>
       </c>
       <c r="D86" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>069</t>
+          <t>148</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C87" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D87" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F87" t="n">
         <v>44.45</v>
@@ -2344,105 +2344,105 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>489</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C88" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>44.35</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C89" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D89" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>44.35</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>079</t>
+          <t>089</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C90" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D90" t="n">
         <v>6</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>588</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C91" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D91" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E91" t="n">
         <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>599</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C92" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -2454,7 +2454,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2464,26 +2464,26 @@
         <v>15</v>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>44.25</v>
+        <v>44.05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C94" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D94" t="n">
         <v>3</v>
@@ -2492,196 +2492,196 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>44.15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>278</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C95" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D95" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>44.1</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>336</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C96" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>44.05</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>013</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C97" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D97" t="n">
         <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>43.95</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>145</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C98" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D98" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E98" t="n">
         <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>43.9</v>
+        <v>43.85</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>678</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C99" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D99" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>288</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C100" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E100" t="n">
         <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>037</t>
+          <t>459</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>88</v>
       </c>
       <c r="C101" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E101" t="n">
         <v>2</v>
       </c>
       <c r="F101" t="n">
-        <v>43.85</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C102" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F102" t="n">
-        <v>43.85</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>155</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C103" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D103" t="n">
         <v>3</v>
@@ -2690,42 +2690,42 @@
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>43.8</v>
+        <v>43.55</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>011</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C104" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D104" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>43.75</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>366</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C105" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D105" t="n">
         <v>11</v>
@@ -2734,900 +2734,900 @@
         <v>1</v>
       </c>
       <c r="F105" t="n">
-        <v>43.75</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>077</t>
+          <t>677</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C106" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D106" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>43.75</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>099</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C107" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D107" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>43.65</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>018</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C108" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>43.6</v>
+        <v>43.15</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>356</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C109" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D109" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" t="n">
-        <v>43.55</v>
+        <v>43.15</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>568</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C110" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E110" t="n">
         <v>1</v>
       </c>
       <c r="F110" t="n">
-        <v>43.5</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>067</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C111" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>43.5</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>577</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C112" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D112" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" t="n">
-        <v>43.3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>089</t>
+          <t>348</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C113" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D113" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>43.25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>057</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C114" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D114" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>43.15</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>558</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C115" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D115" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>43.15</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>029</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C116" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D116" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" t="n">
-        <v>43.1</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>259</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C117" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D117" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>43.05</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C118" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D118" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E118" t="n">
         <v>2</v>
       </c>
       <c r="F118" t="n">
-        <v>43</v>
+        <v>42.75</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>277</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C119" t="n">
         <v>13</v>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>42.95</v>
+        <v>42.55</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>038</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C120" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>42.75</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>059</t>
         </is>
       </c>
       <c r="B121" t="n">
         <v>89</v>
       </c>
       <c r="C121" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>42.65</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>347</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C122" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D122" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>42.6</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>267</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C123" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D123" t="n">
         <v>11</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" t="n">
-        <v>42.6</v>
+        <v>42.35</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>268</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C124" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D124" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>42.55</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>335</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C125" t="n">
         <v>15</v>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>42.45</v>
+        <v>42.25</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>058</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C126" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D126" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E126" t="n">
         <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>42.4</v>
+        <v>42.25</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>258</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C127" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D127" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" t="n">
-        <v>42.35</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>688</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C128" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D128" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>42.35</v>
+        <v>42.15</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>038</t>
+          <t>146</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C129" t="n">
         <v>18</v>
       </c>
       <c r="D129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>058</t>
+          <t>567</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C130" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D130" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>42.25</v>
+        <v>41.95</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>166</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C131" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D131" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>42.25</v>
+        <v>41.95</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C132" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D132" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>42.15</v>
+        <v>41.75</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>068</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C133" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D133" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F133" t="n">
-        <v>41.95</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>478</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C134" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D134" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>41.85</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>236</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C135" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D135" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C136" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D136" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E136" t="n">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>41.8</v>
+        <v>41.65</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>057</t>
+          <t>477</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C137" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D137" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>41.75</v>
+        <v>41.65</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>888</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C138" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D138" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E138" t="n">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>41.75</v>
+        <v>41.55</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>449</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C139" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D139" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>41.7</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>067</t>
+          <t>468</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C140" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D140" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E140" t="n">
         <v>1</v>
       </c>
       <c r="F140" t="n">
-        <v>41.55</v>
+        <v>41.45</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>029</t>
+          <t>667</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C141" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D141" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>41.5</v>
+        <v>41.45</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>088</t>
+          <t>228</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C142" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D142" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>41.35</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>059</t>
+          <t>668</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C143" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D143" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E143" t="n">
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>41.3</v>
+        <v>41.35</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>068</t>
+          <t>088</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C144" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D144" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>41.3</v>
+        <v>41.35</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>016</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C145" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D145" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>41.3</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>355</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C146" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D146" t="n">
         <v>8</v>
@@ -3636,48 +3636,48 @@
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>41.2</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C147" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D147" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E147" t="n">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>41.15</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>233</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C148" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
         <v>41.15</v>
@@ -3686,20 +3686,20 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>345</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C149" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F149" t="n">
         <v>41.1</v>
@@ -3708,17 +3708,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>458</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C150" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E150" t="n">
         <v>0</v>
@@ -3730,14 +3730,14 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>559</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C151" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D151" t="n">
         <v>6</v>
@@ -3746,199 +3746,199 @@
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>41.05</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>066</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C152" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D152" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E152" t="n">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>40.95</v>
+        <v>40.65</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>467</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C153" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" t="n">
-        <v>40.85</v>
+        <v>40.55</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>456</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C154" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D154" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>40.85</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>014</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C155" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>40.8</v>
+        <v>40.45</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>266</t>
         </is>
       </c>
       <c r="B156" t="n">
         <v>84</v>
       </c>
       <c r="C156" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D156" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>40.55</v>
+        <v>40.45</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C157" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D157" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F157" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>036</t>
         </is>
       </c>
       <c r="B158" t="n">
         <v>86</v>
       </c>
       <c r="C158" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D158" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>40.15</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>035</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C159" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D159" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" t="n">
-        <v>40.05</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>028</t>
+          <t>012</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C160" t="n">
         <v>16</v>
       </c>
       <c r="D160" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E160" t="n">
         <v>0</v>
@@ -3950,20 +3950,20 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>036</t>
+          <t>466</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C161" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D161" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161" t="n">
         <v>40</v>
@@ -3972,39 +3972,39 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C162" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E162" t="n">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>40</v>
+        <v>39.95</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>235</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C163" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D163" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
@@ -4016,102 +4016,102 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>007</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C164" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D164" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>39.85</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B165" t="n">
         <v>87</v>
       </c>
       <c r="C165" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D165" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>39.75</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>488</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C166" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D166" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>39.75</v>
+        <v>39.85</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C167" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D167" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>39.75</v>
+        <v>39.85</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>033</t>
+          <t>028</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C168" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D168" t="n">
         <v>5</v>
@@ -4120,42 +4120,42 @@
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>39.75</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>049</t>
+          <t>666</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C169" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D169" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>39.7</v>
+        <v>39.75</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>566</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C170" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D170" t="n">
         <v>6</v>
@@ -4164,101 +4164,101 @@
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>39.6</v>
+        <v>39.75</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>033</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C171" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D171" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>39.6</v>
+        <v>39.75</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>048</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C172" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D172" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>39.55</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>246</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C173" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D173" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F173" t="n">
-        <v>39.5</v>
+        <v>39.45</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C174" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D174" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E174" t="n">
         <v>1</v>
       </c>
       <c r="F174" t="n">
-        <v>39.45</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>457</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -4271,89 +4271,89 @@
         <v>6</v>
       </c>
       <c r="E175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>39.4</v>
+        <v>39.35</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>248</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C176" t="n">
         <v>14</v>
       </c>
       <c r="D176" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>39.35</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>144</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C177" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>257</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C178" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D178" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>39.25</v>
+        <v>39.15</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>557</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C179" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D179" t="n">
         <v>6</v>
@@ -4362,196 +4362,196 @@
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>39.05</v>
+        <v>39.15</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>056</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C180" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>38.8</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>023</t>
+          <t>223</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C181" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>38.65</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>009</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C182" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D182" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>334</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C183" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D183" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>38.35</v>
+        <v>38.65</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>048</t>
+          <t>256</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C184" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D184" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>38.35</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>046</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C185" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D185" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F185" t="n">
-        <v>38.3</v>
+        <v>38.55</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>226</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C186" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D186" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F186" t="n">
-        <v>38.15</v>
+        <v>38.35</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>026</t>
+          <t>023</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C187" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D187" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>37.85</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>247</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C188" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D188" t="n">
         <v>8</v>
@@ -4560,42 +4560,42 @@
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>37.75</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>026</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C189" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D189" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F189" t="n">
-        <v>37.55</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>055</t>
+          <t>556</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C190" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D190" t="n">
         <v>6</v>
@@ -4604,57 +4604,57 @@
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>37.35</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>001</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C191" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D191" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>37.2</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>227</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C192" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D192" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E192" t="n">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>37.15</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>234</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -4664,290 +4664,290 @@
         <v>12</v>
       </c>
       <c r="D193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E193" t="n">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>37</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>455</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C194" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D194" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E194" t="n">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>36.85</v>
+        <v>37.35</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>046</t>
+          <t>446</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C195" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D195" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>36.85</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>055</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C196" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D196" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>36.5</v>
+        <v>37.15</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>034</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C197" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D197" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E197" t="n">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>36.3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>047</t>
+          <t>008</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C198" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D198" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E198" t="n">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>36.15</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>006</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C199" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D199" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E199" t="n">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>36</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>045</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C200" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D200" t="n">
         <v>2</v>
       </c>
       <c r="E200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F200" t="n">
-        <v>35.8</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>447</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C201" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D201" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>034</t>
+          <t>448</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C202" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D202" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E202" t="n">
         <v>0</v>
       </c>
       <c r="F202" t="n">
-        <v>35.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>445</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C203" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D203" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E203" t="n">
         <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>35.5</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>555</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C204" t="n">
+        <v>3</v>
+      </c>
+      <c r="D204" t="n">
         <v>11</v>
       </c>
-      <c r="D204" t="n">
-        <v>2</v>
-      </c>
       <c r="E204" t="n">
         <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>35.45</v>
+        <v>35.65</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>003</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C205" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D205" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E205" t="n">
         <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>35.4</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>025</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C206" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D206" t="n">
         <v>2</v>
@@ -4956,35 +4956,35 @@
         <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>35.3</v>
+        <v>35.45</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>045</t>
+          <t>255</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C207" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D207" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>35.3</v>
+        <v>35.25</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>024</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -5006,29 +5006,29 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>005</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C209" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D209" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E209" t="n">
         <v>0</v>
       </c>
       <c r="F209" t="n">
-        <v>34.8</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>022</t>
+          <t>245</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -5038,48 +5038,48 @@
         <v>10</v>
       </c>
       <c r="D210" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F210" t="n">
-        <v>34.75</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>022</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C211" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F211" t="n">
-        <v>34.4</v>
+        <v>34.75</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>344</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C212" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D212" t="n">
         <v>3</v>
@@ -5088,117 +5088,117 @@
         <v>0</v>
       </c>
       <c r="F212" t="n">
-        <v>34.2</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>222</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C213" t="n">
         <v>6</v>
       </c>
       <c r="D213" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E213" t="n">
         <v>0</v>
       </c>
       <c r="F213" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>224</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C214" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D214" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E214" t="n">
         <v>0</v>
       </c>
       <c r="F214" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>004</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C215" t="n">
         <v>10</v>
       </c>
       <c r="D215" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E215" t="n">
         <v>0</v>
       </c>
       <c r="F215" t="n">
-        <v>33.7</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>002</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C216" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D216" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E216" t="n">
         <v>0</v>
       </c>
       <c r="F216" t="n">
-        <v>32.5</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>225</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C217" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E217" t="n">
         <v>0</v>
       </c>
       <c r="F217" t="n">
-        <v>32.2</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="218">
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C218" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D218" t="n">
         <v>3</v>
@@ -5220,29 +5220,29 @@
         <v>0</v>
       </c>
       <c r="F218" t="n">
-        <v>30.3</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>244</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C219" t="n">
         <v>6</v>
       </c>
       <c r="D219" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E219" t="n">
         <v>0</v>
       </c>
       <c r="F219" t="n">
-        <v>30.1</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="220">
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C220" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
         <v>0</v>
       </c>
       <c r="F220" t="n">
-        <v>29.8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="221">
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
@@ -5286,7 +5286,7 @@
         <v>0</v>
       </c>
       <c r="F221" t="n">
-        <v>27.6</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C2" t="n">
         <v>25</v>
@@ -5359,7 +5359,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>52.35</v>
+        <v>51.95</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -5370,41 +5370,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>51.8</v>
+        <v>51.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>138, 183, 318, 381, 813, 831</t>
+          <t>179, 197, 719, 791, 917, 971</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>379</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
@@ -5413,427 +5413,427 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>179, 197, 719, 791, 917, 971</t>
+          <t>379, 397, 739, 793, 937, 973</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>199</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>50.8</v>
+        <v>50.75</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>189, 198, 819, 891, 918, 981</t>
+          <t>199, 919, 991</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>177</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>101</v>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>50.4</v>
+        <v>50.75</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>379, 397, 739, 793, 937, 973</t>
+          <t>177, 717, 771</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>399</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>50.35</v>
+        <v>50.4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>177, 717, 771</t>
+          <t>399, 939, 993</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>50.35</v>
+        <v>50.25</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>199, 919, 991</t>
+          <t>138, 183, 318, 381, 813, 831</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>129, 192, 219, 291, 912, 921</t>
+          <t>137, 173, 317, 371, 713, 731</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>189</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>50.3</v>
+        <v>50.05</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>137, 173, 317, 371, 713, 731</t>
+          <t>189, 198, 819, 891, 918, 981</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>50.1</v>
+        <v>49.9</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>389, 398, 839, 893, 938, 983</t>
+          <t>129, 192, 219, 291, 912, 921</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>369</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>50</v>
+        <v>49.85</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>399, 939, 993</t>
+          <t>369, 396, 639, 693, 936, 963</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>389</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>49.85</v>
+        <v>49.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>369, 396, 639, 693, 936, 963</t>
+          <t>389, 398, 839, 893, 938, 983</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C14" t="n">
         <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>378, 387, 738, 783, 837, 873</t>
+          <t>299, 929, 992</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>378</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>178, 187, 718, 781, 817, 871</t>
+          <t>378, 387, 738, 783, 837, 873</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>49.65</v>
+        <v>49.35</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>339, 393, 933</t>
+          <t>119, 191, 911</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>699</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>49.6</v>
+        <v>49.25</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>159, 195, 519, 591, 915, 951</t>
+          <t>699, 969, 996</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>339</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>49.6</v>
+        <v>49.25</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>113, 131, 311</t>
+          <t>339, 393, 933</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>49.55</v>
+        <v>49.2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>158, 185, 518, 581, 815, 851</t>
+          <t>159, 195, 519, 591, 915, 951</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>799</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C20" t="n">
         <v>17</v>
@@ -5842,41 +5842,41 @@
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>49.55</v>
+        <v>49.2</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>119, 191, 911</t>
+          <t>799, 979, 997</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>49.5</v>
+        <v>48.95</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>239, 293, 329, 392, 923, 932</t>
+          <t>178, 187, 718, 781, 817, 871</t>
         </is>
       </c>
     </row>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C22" t="n">
         <v>21</v>
@@ -5899,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>49.35</v>
+        <v>48.95</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5910,95 +5910,95 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>239</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>49.2</v>
+        <v>48.75</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>299, 929, 992</t>
+          <t>239, 293, 329, 392, 923, 932</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D24" t="n">
         <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>49.15</v>
+        <v>48.65</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>118, 181, 811</t>
+          <t>169, 196, 619, 691, 916, 961</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>149</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C25" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" t="n">
         <v>2</v>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
       <c r="F25" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>135, 153, 315, 351, 513, 531</t>
+          <t>149, 194, 419, 491, 914, 941</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>377</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C26" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D26" t="n">
         <v>6</v>
@@ -6007,11 +6007,11 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>48.65</v>
+        <v>48.5</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>169, 196, 619, 691, 916, 961</t>
+          <t>377, 737, 773</t>
         </is>
       </c>
     </row>
